--- a/econ.research_v1.xlsx
+++ b/econ.research_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emelindo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A51EF-D509-41F5-964E-3BB3CE3F42A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C82712F-20E1-41DC-8BB7-F182F70CA386}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{21D0CDA9-0CA1-4A29-83F3-EAB7B1B086B7}"/>
   </bookViews>
@@ -38,33 +38,9 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Ranking</t>
-  </si>
-  <si>
-    <t>Matches Played</t>
-  </si>
-  <si>
     <t>Alcaraz</t>
   </si>
   <si>
-    <t>Height (cm)</t>
-  </si>
-  <si>
-    <t>Racket Head Size (cm^2)</t>
-  </si>
-  <si>
-    <t>Right Handed (1)</t>
-  </si>
-  <si>
-    <t>1st Serve%</t>
-  </si>
-  <si>
-    <t>Double Faults</t>
-  </si>
-  <si>
     <t>Sinner</t>
   </si>
   <si>
@@ -362,7 +338,31 @@
     <t>Schoolkate</t>
   </si>
   <si>
-    <t>Avg 1st Serve Speed</t>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>hgt</t>
+  </si>
+  <si>
+    <t>rhand</t>
+  </si>
+  <si>
+    <t>mtch</t>
+  </si>
+  <si>
+    <t>rhsize</t>
+  </si>
+  <si>
+    <t>1serve</t>
+  </si>
+  <si>
+    <t>2faults</t>
+  </si>
+  <si>
+    <t>avgspeed</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0456E88D-A36A-4B1D-B7E4-7DD5B41E26EE}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -736,44 +736,44 @@
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -799,13 +799,13 @@
       <c r="I2">
         <v>219</v>
       </c>
-      <c r="K2">
+      <c r="J2">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -831,13 +831,13 @@
       <c r="I3">
         <v>91</v>
       </c>
-      <c r="K3">
+      <c r="J3">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -863,13 +863,13 @@
       <c r="I4">
         <v>152</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -895,13 +895,13 @@
       <c r="I5">
         <v>102</v>
       </c>
-      <c r="K5">
+      <c r="J5">
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -927,13 +927,13 @@
       <c r="I6">
         <v>234</v>
       </c>
-      <c r="K6">
+      <c r="J6">
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -959,13 +959,13 @@
       <c r="I7">
         <v>146</v>
       </c>
-      <c r="K7">
+      <c r="J7">
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -991,13 +991,13 @@
       <c r="I8">
         <v>185</v>
       </c>
-      <c r="K8">
+      <c r="J8">
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
@@ -1023,13 +1023,13 @@
       <c r="I9">
         <v>134</v>
       </c>
-      <c r="K9">
+      <c r="J9">
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -1055,13 +1055,13 @@
       <c r="I10">
         <v>198</v>
       </c>
-      <c r="K10">
+      <c r="J10">
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -1087,13 +1087,13 @@
       <c r="I11">
         <v>100</v>
       </c>
-      <c r="K11">
+      <c r="J11">
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
@@ -1119,13 +1119,13 @@
       <c r="I12">
         <v>299</v>
       </c>
-      <c r="K12">
+      <c r="J12">
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
@@ -1151,13 +1151,13 @@
       <c r="I13">
         <v>112</v>
       </c>
-      <c r="K13">
+      <c r="J13">
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
@@ -1183,13 +1183,13 @@
       <c r="I14">
         <v>277</v>
       </c>
-      <c r="K14">
+      <c r="J14">
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
@@ -1215,13 +1215,13 @@
       <c r="I15">
         <v>152</v>
       </c>
-      <c r="K15">
+      <c r="J15">
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -1247,13 +1247,13 @@
       <c r="I16">
         <v>152</v>
       </c>
-      <c r="K16">
+      <c r="J16">
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>16</v>
@@ -1279,13 +1279,13 @@
       <c r="I17">
         <v>178</v>
       </c>
-      <c r="K17">
+      <c r="J17">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
@@ -1311,13 +1311,13 @@
       <c r="I18">
         <v>135</v>
       </c>
-      <c r="K18">
+      <c r="J18">
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
@@ -1343,13 +1343,13 @@
       <c r="I19">
         <v>139</v>
       </c>
-      <c r="K19">
+      <c r="J19">
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
@@ -1375,13 +1375,13 @@
       <c r="I20">
         <v>199</v>
       </c>
-      <c r="K20">
+      <c r="J20">
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>20</v>
@@ -1407,13 +1407,13 @@
       <c r="I21">
         <v>104</v>
       </c>
-      <c r="K21">
+      <c r="J21">
         <v>187</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2">
         <v>21</v>
@@ -1439,13 +1439,13 @@
       <c r="I22">
         <v>172</v>
       </c>
-      <c r="K22">
+      <c r="J22">
         <v>185</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2">
         <v>22</v>
@@ -1471,10 +1471,13 @@
       <c r="I23">
         <v>189</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>23</v>
@@ -1500,13 +1503,13 @@
       <c r="I24">
         <v>302</v>
       </c>
-      <c r="K24">
+      <c r="J24">
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>24</v>
@@ -1532,13 +1535,13 @@
       <c r="I25">
         <v>87</v>
       </c>
-      <c r="K25">
+      <c r="J25">
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>25</v>
@@ -1564,13 +1567,13 @@
       <c r="I26">
         <v>164</v>
       </c>
-      <c r="K26">
+      <c r="J26">
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>26</v>
@@ -1596,13 +1599,13 @@
       <c r="I27">
         <v>167</v>
       </c>
-      <c r="K27">
+      <c r="J27">
         <v>193</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>27</v>
@@ -1628,13 +1631,13 @@
       <c r="I28">
         <v>140</v>
       </c>
-      <c r="K28">
+      <c r="J28">
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>28</v>
@@ -1660,13 +1663,13 @@
       <c r="I29">
         <v>227</v>
       </c>
-      <c r="K29">
+      <c r="J29">
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>29</v>
@@ -1692,13 +1695,13 @@
       <c r="I30">
         <v>179</v>
       </c>
-      <c r="K30">
+      <c r="J30">
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>30</v>
@@ -1724,13 +1727,13 @@
       <c r="I31">
         <v>129</v>
       </c>
-      <c r="K31">
+      <c r="J31">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>31</v>
@@ -1756,13 +1759,13 @@
       <c r="I32">
         <v>37</v>
       </c>
-      <c r="K32">
+      <c r="J32">
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>32</v>
@@ -1788,10 +1791,13 @@
       <c r="I33">
         <v>137</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>33</v>
@@ -1817,13 +1823,13 @@
       <c r="I34">
         <v>166</v>
       </c>
-      <c r="K34">
+      <c r="J34">
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>34</v>
@@ -1849,13 +1855,13 @@
       <c r="I35">
         <v>152</v>
       </c>
-      <c r="K35">
+      <c r="J35">
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>35</v>
@@ -1881,13 +1887,13 @@
       <c r="I36">
         <v>67</v>
       </c>
-      <c r="K36">
+      <c r="J36">
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>36</v>
@@ -1913,10 +1919,13 @@
       <c r="I37">
         <v>127</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J37">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>37</v>
@@ -1942,13 +1951,13 @@
       <c r="I38">
         <v>107</v>
       </c>
-      <c r="K38">
+      <c r="J38">
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>38</v>
@@ -1974,10 +1983,13 @@
       <c r="I39">
         <v>148</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J39">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>39</v>
@@ -2003,13 +2015,13 @@
       <c r="I40">
         <v>90</v>
       </c>
-      <c r="K40">
+      <c r="J40">
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
         <v>40</v>
@@ -2035,10 +2047,13 @@
       <c r="I41">
         <v>128</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J41">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
         <v>41</v>
@@ -2064,13 +2079,13 @@
       <c r="I42">
         <v>132</v>
       </c>
-      <c r="K42">
+      <c r="J42">
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
         <v>42</v>
@@ -2096,10 +2111,13 @@
       <c r="I43">
         <v>222</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2">
         <v>43</v>
@@ -2125,10 +2143,13 @@
       <c r="I44">
         <v>132</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J44">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2">
         <v>44</v>
@@ -2154,10 +2175,13 @@
       <c r="I45">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J45">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2">
         <v>45</v>
@@ -2183,10 +2207,13 @@
       <c r="I46">
         <v>78</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2">
         <v>46</v>
@@ -2212,10 +2239,13 @@
       <c r="I47">
         <v>120</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2">
         <v>47</v>
@@ -2241,10 +2271,13 @@
       <c r="I48">
         <v>134</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J48">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>48</v>
@@ -2270,13 +2303,13 @@
       <c r="I49">
         <v>99</v>
       </c>
-      <c r="K49">
+      <c r="J49">
         <v>188</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
         <v>49</v>
@@ -2302,10 +2335,13 @@
       <c r="I50">
         <v>124</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
         <v>50</v>
@@ -2331,10 +2367,13 @@
       <c r="I51">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2">
         <v>51</v>
@@ -2360,10 +2399,13 @@
       <c r="I52">
         <v>128</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2">
         <v>52</v>
@@ -2389,10 +2431,13 @@
       <c r="I53">
         <v>198</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J53">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2">
         <v>53</v>
@@ -2418,10 +2463,13 @@
       <c r="I54">
         <v>133</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J54">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2">
         <v>54</v>
@@ -2447,10 +2495,13 @@
       <c r="I55">
         <v>117</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J55">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2">
         <v>55</v>
@@ -2476,10 +2527,13 @@
       <c r="I56">
         <v>76</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J56">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2">
         <v>56</v>
@@ -2505,10 +2559,13 @@
       <c r="I57">
         <v>57</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J57">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
         <v>57</v>
@@ -2534,10 +2591,13 @@
       <c r="I58">
         <v>46</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J58">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
         <v>58</v>
@@ -2563,13 +2623,13 @@
       <c r="I59">
         <v>176</v>
       </c>
-      <c r="K59">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J59">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2">
         <v>59</v>
@@ -2595,13 +2655,13 @@
       <c r="I60">
         <v>86</v>
       </c>
-      <c r="K60">
+      <c r="J60">
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2">
         <v>60</v>
@@ -2627,10 +2687,13 @@
       <c r="I61">
         <v>134</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J61">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2">
         <v>61</v>
@@ -2656,10 +2719,13 @@
       <c r="I62">
         <v>141</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J62">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B63" s="2">
         <v>62</v>
@@ -2685,10 +2751,13 @@
       <c r="I63">
         <v>50</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J63">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2">
         <v>63</v>
@@ -2714,10 +2783,13 @@
       <c r="I64">
         <v>65</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J64">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2">
         <v>64</v>
@@ -2743,10 +2815,13 @@
       <c r="I65">
         <v>82</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J65">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B66" s="2">
         <v>65</v>
@@ -2772,10 +2847,13 @@
       <c r="I66">
         <v>86</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J66">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B67" s="2">
         <v>66</v>
@@ -2801,10 +2879,13 @@
       <c r="I67">
         <v>114</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J67">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B68" s="2">
         <v>67</v>
@@ -2830,10 +2911,13 @@
       <c r="I68">
         <v>145</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J68">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B69" s="2">
         <v>68</v>
@@ -2859,10 +2943,13 @@
       <c r="I69">
         <v>185</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J69">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B70" s="2">
         <v>69</v>
@@ -2888,10 +2975,13 @@
       <c r="I70">
         <v>54</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J70">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B71" s="2">
         <v>70</v>
@@ -2917,10 +3007,13 @@
       <c r="I71">
         <v>95</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J71">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2">
         <v>71</v>
@@ -2946,10 +3039,13 @@
       <c r="I72">
         <v>210</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J72">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2">
         <v>72</v>
@@ -2975,13 +3071,13 @@
       <c r="I73">
         <v>35</v>
       </c>
-      <c r="K73">
+      <c r="J73">
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2">
         <v>73</v>
@@ -3007,10 +3103,13 @@
       <c r="I74">
         <v>53</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J74">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2">
         <v>74</v>
@@ -3036,10 +3135,13 @@
       <c r="I75">
         <v>93</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J75">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2">
         <v>75</v>
@@ -3065,10 +3167,13 @@
       <c r="I76">
         <v>105</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J76">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2">
         <v>76</v>
@@ -3094,10 +3199,13 @@
       <c r="I77">
         <v>94</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J77">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2">
         <v>77</v>
@@ -3123,10 +3231,13 @@
       <c r="I78">
         <v>173</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J78">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2">
         <v>78</v>
@@ -3152,10 +3263,13 @@
       <c r="I79">
         <v>112</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J79">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2">
         <v>79</v>
@@ -3181,10 +3295,13 @@
       <c r="I80">
         <v>18</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J80">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2">
         <v>80</v>
@@ -3210,10 +3327,13 @@
       <c r="I81">
         <v>55</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J81">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2">
         <v>81</v>
@@ -3239,10 +3359,13 @@
       <c r="I82">
         <v>93</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J82">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2">
         <v>82</v>
@@ -3268,13 +3391,13 @@
       <c r="I83">
         <v>69</v>
       </c>
-      <c r="K83">
+      <c r="J83">
         <v>183</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2">
         <v>83</v>
@@ -3300,10 +3423,13 @@
       <c r="I84">
         <v>122</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J84">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2">
         <v>84</v>
@@ -3329,10 +3455,13 @@
       <c r="I85">
         <v>98</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J85">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2">
         <v>85</v>
@@ -3358,10 +3487,13 @@
       <c r="I86">
         <v>114</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J86">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2">
         <v>86</v>
@@ -3387,10 +3519,13 @@
       <c r="I87">
         <v>57</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J87">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B88" s="2">
         <v>87</v>
@@ -3416,10 +3551,13 @@
       <c r="I88">
         <v>64</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J88">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B89" s="2">
         <v>88</v>
@@ -3445,10 +3583,13 @@
       <c r="I89">
         <v>57</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J89">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B90" s="2">
         <v>89</v>
@@ -3474,10 +3615,13 @@
       <c r="I90">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J90">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B91" s="2">
         <v>90</v>
@@ -3503,10 +3647,13 @@
       <c r="I91">
         <v>79</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J91">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B92" s="2">
         <v>91</v>
@@ -3532,10 +3679,13 @@
       <c r="I92">
         <v>163</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J92">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B93" s="2">
         <v>92</v>
@@ -3561,10 +3711,13 @@
       <c r="I93">
         <v>129</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J93">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B94" s="2">
         <v>93</v>
@@ -3590,10 +3743,13 @@
       <c r="I94">
         <v>37</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J94">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B95" s="2">
         <v>94</v>
@@ -3619,10 +3775,13 @@
       <c r="I95">
         <v>80</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J95">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B96" s="2">
         <v>95</v>
@@ -3648,10 +3807,13 @@
       <c r="I96">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B97" s="2">
         <v>96</v>
@@ -3677,10 +3839,13 @@
       <c r="I97">
         <v>66</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2">
         <v>97</v>
@@ -3706,10 +3871,13 @@
       <c r="I98">
         <v>88</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B99" s="2">
         <v>98</v>
@@ -3735,10 +3903,13 @@
       <c r="I99">
         <v>74</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B100" s="2">
         <v>99</v>
@@ -3764,10 +3935,13 @@
       <c r="I100">
         <v>40</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2">
         <v>100</v>
@@ -3792,6 +3966,9 @@
       </c>
       <c r="I101">
         <v>68</v>
+      </c>
+      <c r="J101">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/econ.research_v1.xlsx
+++ b/econ.research_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emelindo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C82712F-20E1-41DC-8BB7-F182F70CA386}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AFAF38-9F8E-441E-9F37-9CFD285FF6BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{21D0CDA9-0CA1-4A29-83F3-EAB7B1B086B7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{21D0CDA9-0CA1-4A29-83F3-EAB7B1B086B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>

--- a/econ.research_v1.xlsx
+++ b/econ.research_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emelindo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A51EF-D509-41F5-964E-3BB3CE3F42A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{623FE0C5-D120-4BFD-9A60-8AE33B04FC95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{21D0CDA9-0CA1-4A29-83F3-EAB7B1B086B7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{21D0CDA9-0CA1-4A29-83F3-EAB7B1B086B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -38,33 +38,9 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Ranking</t>
-  </si>
-  <si>
-    <t>Matches Played</t>
-  </si>
-  <si>
     <t>Alcaraz</t>
   </si>
   <si>
-    <t>Height (cm)</t>
-  </si>
-  <si>
-    <t>Racket Head Size (cm^2)</t>
-  </si>
-  <si>
-    <t>Right Handed (1)</t>
-  </si>
-  <si>
-    <t>1st Serve%</t>
-  </si>
-  <si>
-    <t>Double Faults</t>
-  </si>
-  <si>
     <t>Sinner</t>
   </si>
   <si>
@@ -362,7 +338,31 @@
     <t>Schoolkate</t>
   </si>
   <si>
-    <t>Avg 1st Serve Speed</t>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>hgt</t>
+  </si>
+  <si>
+    <t>rhand</t>
+  </si>
+  <si>
+    <t>mtch</t>
+  </si>
+  <si>
+    <t>rhsize</t>
+  </si>
+  <si>
+    <t>1serve</t>
+  </si>
+  <si>
+    <t>2faults</t>
+  </si>
+  <si>
+    <t>avgspeed</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0456E88D-A36A-4B1D-B7E4-7DD5B41E26EE}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -736,44 +736,44 @@
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -799,13 +799,13 @@
       <c r="I2">
         <v>219</v>
       </c>
-      <c r="K2">
+      <c r="J2">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -831,13 +831,13 @@
       <c r="I3">
         <v>91</v>
       </c>
-      <c r="K3">
+      <c r="J3">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -863,13 +863,13 @@
       <c r="I4">
         <v>152</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -895,13 +895,13 @@
       <c r="I5">
         <v>102</v>
       </c>
-      <c r="K5">
+      <c r="J5">
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -927,13 +927,13 @@
       <c r="I6">
         <v>234</v>
       </c>
-      <c r="K6">
+      <c r="J6">
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -959,13 +959,13 @@
       <c r="I7">
         <v>146</v>
       </c>
-      <c r="K7">
+      <c r="J7">
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -991,13 +991,13 @@
       <c r="I8">
         <v>185</v>
       </c>
-      <c r="K8">
+      <c r="J8">
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
@@ -1023,13 +1023,13 @@
       <c r="I9">
         <v>134</v>
       </c>
-      <c r="K9">
+      <c r="J9">
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -1055,13 +1055,13 @@
       <c r="I10">
         <v>198</v>
       </c>
-      <c r="K10">
+      <c r="J10">
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -1087,13 +1087,13 @@
       <c r="I11">
         <v>100</v>
       </c>
-      <c r="K11">
+      <c r="J11">
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
@@ -1119,13 +1119,13 @@
       <c r="I12">
         <v>299</v>
       </c>
-      <c r="K12">
+      <c r="J12">
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
@@ -1151,13 +1151,13 @@
       <c r="I13">
         <v>112</v>
       </c>
-      <c r="K13">
+      <c r="J13">
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
@@ -1183,13 +1183,13 @@
       <c r="I14">
         <v>277</v>
       </c>
-      <c r="K14">
+      <c r="J14">
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
@@ -1215,13 +1215,13 @@
       <c r="I15">
         <v>152</v>
       </c>
-      <c r="K15">
+      <c r="J15">
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -1247,13 +1247,13 @@
       <c r="I16">
         <v>152</v>
       </c>
-      <c r="K16">
+      <c r="J16">
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>16</v>
@@ -1279,13 +1279,13 @@
       <c r="I17">
         <v>178</v>
       </c>
-      <c r="K17">
+      <c r="J17">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
@@ -1311,13 +1311,13 @@
       <c r="I18">
         <v>135</v>
       </c>
-      <c r="K18">
+      <c r="J18">
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
@@ -1343,13 +1343,13 @@
       <c r="I19">
         <v>139</v>
       </c>
-      <c r="K19">
+      <c r="J19">
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
@@ -1375,13 +1375,13 @@
       <c r="I20">
         <v>199</v>
       </c>
-      <c r="K20">
+      <c r="J20">
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>20</v>
@@ -1407,13 +1407,13 @@
       <c r="I21">
         <v>104</v>
       </c>
-      <c r="K21">
+      <c r="J21">
         <v>187</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2">
         <v>21</v>
@@ -1439,13 +1439,13 @@
       <c r="I22">
         <v>172</v>
       </c>
-      <c r="K22">
+      <c r="J22">
         <v>185</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2">
         <v>22</v>
@@ -1471,10 +1471,13 @@
       <c r="I23">
         <v>189</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>23</v>
@@ -1500,13 +1503,13 @@
       <c r="I24">
         <v>302</v>
       </c>
-      <c r="K24">
+      <c r="J24">
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>24</v>
@@ -1532,13 +1535,13 @@
       <c r="I25">
         <v>87</v>
       </c>
-      <c r="K25">
+      <c r="J25">
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>25</v>
@@ -1564,13 +1567,13 @@
       <c r="I26">
         <v>164</v>
       </c>
-      <c r="K26">
+      <c r="J26">
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>26</v>
@@ -1596,13 +1599,13 @@
       <c r="I27">
         <v>167</v>
       </c>
-      <c r="K27">
+      <c r="J27">
         <v>193</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>27</v>
@@ -1628,13 +1631,13 @@
       <c r="I28">
         <v>140</v>
       </c>
-      <c r="K28">
+      <c r="J28">
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>28</v>
@@ -1660,13 +1663,13 @@
       <c r="I29">
         <v>227</v>
       </c>
-      <c r="K29">
+      <c r="J29">
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>29</v>
@@ -1692,13 +1695,13 @@
       <c r="I30">
         <v>179</v>
       </c>
-      <c r="K30">
+      <c r="J30">
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>30</v>
@@ -1724,13 +1727,13 @@
       <c r="I31">
         <v>129</v>
       </c>
-      <c r="K31">
+      <c r="J31">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>31</v>
@@ -1756,13 +1759,13 @@
       <c r="I32">
         <v>37</v>
       </c>
-      <c r="K32">
+      <c r="J32">
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>32</v>
@@ -1788,10 +1791,13 @@
       <c r="I33">
         <v>137</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>33</v>
@@ -1817,13 +1823,13 @@
       <c r="I34">
         <v>166</v>
       </c>
-      <c r="K34">
+      <c r="J34">
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>34</v>
@@ -1849,13 +1855,13 @@
       <c r="I35">
         <v>152</v>
       </c>
-      <c r="K35">
+      <c r="J35">
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>35</v>
@@ -1881,13 +1887,13 @@
       <c r="I36">
         <v>67</v>
       </c>
-      <c r="K36">
+      <c r="J36">
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>36</v>
@@ -1913,10 +1919,13 @@
       <c r="I37">
         <v>127</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J37">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>37</v>
@@ -1942,13 +1951,13 @@
       <c r="I38">
         <v>107</v>
       </c>
-      <c r="K38">
+      <c r="J38">
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>38</v>
@@ -1974,10 +1983,13 @@
       <c r="I39">
         <v>148</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J39">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>39</v>
@@ -2003,13 +2015,13 @@
       <c r="I40">
         <v>90</v>
       </c>
-      <c r="K40">
+      <c r="J40">
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
         <v>40</v>
@@ -2035,10 +2047,13 @@
       <c r="I41">
         <v>128</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J41">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
         <v>41</v>
@@ -2064,13 +2079,13 @@
       <c r="I42">
         <v>132</v>
       </c>
-      <c r="K42">
+      <c r="J42">
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
         <v>42</v>
@@ -2096,10 +2111,13 @@
       <c r="I43">
         <v>222</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2">
         <v>43</v>
@@ -2125,10 +2143,13 @@
       <c r="I44">
         <v>132</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J44">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2">
         <v>44</v>
@@ -2154,10 +2175,13 @@
       <c r="I45">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J45">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2">
         <v>45</v>
@@ -2183,10 +2207,13 @@
       <c r="I46">
         <v>78</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2">
         <v>46</v>
@@ -2212,10 +2239,13 @@
       <c r="I47">
         <v>120</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2">
         <v>47</v>
@@ -2241,10 +2271,13 @@
       <c r="I48">
         <v>134</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J48">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>48</v>
@@ -2270,13 +2303,13 @@
       <c r="I49">
         <v>99</v>
       </c>
-      <c r="K49">
+      <c r="J49">
         <v>188</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
         <v>49</v>
@@ -2302,10 +2335,13 @@
       <c r="I50">
         <v>124</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
         <v>50</v>
@@ -2331,10 +2367,13 @@
       <c r="I51">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2">
         <v>51</v>
@@ -2360,10 +2399,13 @@
       <c r="I52">
         <v>128</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2">
         <v>52</v>
@@ -2389,10 +2431,13 @@
       <c r="I53">
         <v>198</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J53">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2">
         <v>53</v>
@@ -2418,10 +2463,13 @@
       <c r="I54">
         <v>133</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J54">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2">
         <v>54</v>
@@ -2447,10 +2495,13 @@
       <c r="I55">
         <v>117</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J55">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2">
         <v>55</v>
@@ -2476,10 +2527,13 @@
       <c r="I56">
         <v>76</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J56">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2">
         <v>56</v>
@@ -2505,10 +2559,13 @@
       <c r="I57">
         <v>57</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J57">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
         <v>57</v>
@@ -2534,10 +2591,13 @@
       <c r="I58">
         <v>46</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J58">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
         <v>58</v>
@@ -2563,13 +2623,13 @@
       <c r="I59">
         <v>176</v>
       </c>
-      <c r="K59">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J59">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2">
         <v>59</v>
@@ -2595,13 +2655,13 @@
       <c r="I60">
         <v>86</v>
       </c>
-      <c r="K60">
+      <c r="J60">
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2">
         <v>60</v>
@@ -2627,10 +2687,13 @@
       <c r="I61">
         <v>134</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J61">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2">
         <v>61</v>
@@ -2656,10 +2719,13 @@
       <c r="I62">
         <v>141</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J62">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B63" s="2">
         <v>62</v>
@@ -2685,10 +2751,13 @@
       <c r="I63">
         <v>50</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J63">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2">
         <v>63</v>
@@ -2714,10 +2783,13 @@
       <c r="I64">
         <v>65</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J64">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2">
         <v>64</v>
@@ -2743,10 +2815,13 @@
       <c r="I65">
         <v>82</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J65">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B66" s="2">
         <v>65</v>
@@ -2772,10 +2847,13 @@
       <c r="I66">
         <v>86</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J66">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B67" s="2">
         <v>66</v>
@@ -2801,10 +2879,13 @@
       <c r="I67">
         <v>114</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J67">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B68" s="2">
         <v>67</v>
@@ -2830,10 +2911,13 @@
       <c r="I68">
         <v>145</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J68">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B69" s="2">
         <v>68</v>
@@ -2859,10 +2943,13 @@
       <c r="I69">
         <v>185</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J69">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B70" s="2">
         <v>69</v>
@@ -2888,10 +2975,13 @@
       <c r="I70">
         <v>54</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J70">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B71" s="2">
         <v>70</v>
@@ -2917,10 +3007,13 @@
       <c r="I71">
         <v>95</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J71">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2">
         <v>71</v>
@@ -2946,10 +3039,13 @@
       <c r="I72">
         <v>210</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J72">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2">
         <v>72</v>
@@ -2975,13 +3071,13 @@
       <c r="I73">
         <v>35</v>
       </c>
-      <c r="K73">
+      <c r="J73">
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2">
         <v>73</v>
@@ -3007,10 +3103,13 @@
       <c r="I74">
         <v>53</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J74">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2">
         <v>74</v>
@@ -3036,10 +3135,13 @@
       <c r="I75">
         <v>93</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J75">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2">
         <v>75</v>
@@ -3065,10 +3167,13 @@
       <c r="I76">
         <v>105</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J76">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2">
         <v>76</v>
@@ -3094,10 +3199,13 @@
       <c r="I77">
         <v>94</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J77">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2">
         <v>77</v>
@@ -3123,10 +3231,13 @@
       <c r="I78">
         <v>173</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J78">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2">
         <v>78</v>
@@ -3152,10 +3263,13 @@
       <c r="I79">
         <v>112</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J79">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2">
         <v>79</v>
@@ -3181,10 +3295,13 @@
       <c r="I80">
         <v>18</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J80">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2">
         <v>80</v>
@@ -3210,10 +3327,13 @@
       <c r="I81">
         <v>55</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J81">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2">
         <v>81</v>
@@ -3239,10 +3359,13 @@
       <c r="I82">
         <v>93</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J82">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2">
         <v>82</v>
@@ -3268,13 +3391,13 @@
       <c r="I83">
         <v>69</v>
       </c>
-      <c r="K83">
+      <c r="J83">
         <v>183</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2">
         <v>83</v>
@@ -3300,10 +3423,13 @@
       <c r="I84">
         <v>122</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J84">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2">
         <v>84</v>
@@ -3329,10 +3455,13 @@
       <c r="I85">
         <v>98</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J85">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2">
         <v>85</v>
@@ -3358,10 +3487,13 @@
       <c r="I86">
         <v>114</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J86">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2">
         <v>86</v>
@@ -3387,10 +3519,13 @@
       <c r="I87">
         <v>57</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J87">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B88" s="2">
         <v>87</v>
@@ -3416,10 +3551,13 @@
       <c r="I88">
         <v>64</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J88">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B89" s="2">
         <v>88</v>
@@ -3445,10 +3583,13 @@
       <c r="I89">
         <v>57</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J89">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B90" s="2">
         <v>89</v>
@@ -3474,10 +3615,13 @@
       <c r="I90">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J90">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B91" s="2">
         <v>90</v>
@@ -3503,10 +3647,13 @@
       <c r="I91">
         <v>79</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J91">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B92" s="2">
         <v>91</v>
@@ -3532,10 +3679,13 @@
       <c r="I92">
         <v>163</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J92">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B93" s="2">
         <v>92</v>
@@ -3561,10 +3711,13 @@
       <c r="I93">
         <v>129</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J93">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B94" s="2">
         <v>93</v>
@@ -3590,10 +3743,13 @@
       <c r="I94">
         <v>37</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J94">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B95" s="2">
         <v>94</v>
@@ -3619,10 +3775,13 @@
       <c r="I95">
         <v>80</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J95">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B96" s="2">
         <v>95</v>
@@ -3648,10 +3807,13 @@
       <c r="I96">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B97" s="2">
         <v>96</v>
@@ -3677,10 +3839,13 @@
       <c r="I97">
         <v>66</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2">
         <v>97</v>
@@ -3706,10 +3871,13 @@
       <c r="I98">
         <v>88</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B99" s="2">
         <v>98</v>
@@ -3735,10 +3903,13 @@
       <c r="I99">
         <v>74</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B100" s="2">
         <v>99</v>
@@ -3764,10 +3935,13 @@
       <c r="I100">
         <v>40</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2">
         <v>100</v>
@@ -3792,6 +3966,9 @@
       </c>
       <c r="I101">
         <v>68</v>
+      </c>
+      <c r="J101">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
